--- a/Flexibility_Preferences.xlsx
+++ b/Flexibility_Preferences.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dariovezzali/Development/Pandas-Biogeme/Pandas-Biogeme/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABAEF7B-7969-F543-B227-7435FAFD692C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D187C4-3505-6242-A49F-64AFA071988D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19940" xr2:uid="{ADD43ED2-A73A-FE49-A984-2AB27DA5AEBD}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19940" activeTab="12" xr2:uid="{ADD43ED2-A73A-FE49-A984-2AB27DA5AEBD}"/>
   </bookViews>
   <sheets>
     <sheet name="House_01" sheetId="14" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="97">
   <si>
     <t>ac_1</t>
   </si>
@@ -397,6 +397,9 @@
   <si>
     <t>Model 3 – Appliance-specific</t>
   </si>
+  <si>
+    <t>Model 1 – Generic – EQUIVALENT TO MODEL 3</t>
+  </si>
 </sst>
 </file>
 
@@ -569,400 +572,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="86">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="48">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1883,33 +1506,33 @@
       <c r="F8" s="2"/>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="J10" s="26" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="J10" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="R10" s="26" t="s">
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="R10" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B11" s="11" t="s">
@@ -2757,15 +2380,15 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
       <c r="J24" s="2">
         <v>12</v>
       </c>
@@ -2966,15 +2589,15 @@
       <c r="C28" s="20">
         <v>-449.66449999999998</v>
       </c>
-      <c r="J28" s="28" t="s">
+      <c r="J28" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
       <c r="R28" s="2">
         <v>16</v>
       </c>
@@ -3126,26 +2749,26 @@
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
-      <c r="R32" s="28" t="s">
+      <c r="R32" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="26"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="26"/>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
       <c r="J33" t="s">
         <v>73</v>
       </c>
@@ -3224,15 +2847,15 @@
         <f>-2*(C28-K32)</f>
         <v>229.66879999999992</v>
       </c>
-      <c r="J37" s="29" t="s">
+      <c r="J37" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
       <c r="R37" t="s">
         <v>73</v>
       </c>
@@ -3251,13 +2874,13 @@
       <c r="D38" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="27" t="str">
+      <c r="E38" s="29" t="str">
         <f>IF(C37&lt;C38,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
       <c r="J38" s="30" t="s">
         <v>67</v>
       </c>
@@ -3310,41 +2933,41 @@
       <c r="L42" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="M42" s="27" t="str">
+      <c r="M42" s="29" t="str">
         <f>IF(K41&lt;K42,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 cannot be rejected</v>
       </c>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="R32:X32"/>
-    <mergeCell ref="J37:P37"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="R10:X10"/>
-    <mergeCell ref="M42:P42"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="J28:P28"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="J38:P38"/>
+    <mergeCell ref="R32:X32"/>
+    <mergeCell ref="J37:P37"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="R10:X10"/>
+    <mergeCell ref="M42:P42"/>
   </mergeCells>
   <conditionalFormatting sqref="E38:H38">
-    <cfRule type="cellIs" dxfId="83" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42:P42">
-    <cfRule type="cellIs" dxfId="79" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3475,33 +3098,33 @@
       <c r="F9" s="2"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="J11" s="26" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="J11" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="R11" s="26" t="s">
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="R11" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="26"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
@@ -4414,15 +4037,15 @@
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
       <c r="J26" s="10">
         <v>13</v>
       </c>
@@ -4818,15 +4441,15 @@
       </c>
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="J34" s="28" t="s">
+      <c r="J34" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="28"/>
-      <c r="P34" s="28"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
       <c r="R34" s="10">
         <v>21</v>
       </c>
@@ -4984,15 +4607,15 @@
       <c r="M38" s="12"/>
       <c r="N38" s="12"/>
       <c r="O38" s="12"/>
-      <c r="R38" s="28" t="s">
+      <c r="R38" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
-      <c r="V38" s="28"/>
-      <c r="W38" s="28"/>
-      <c r="X38" s="28"/>
+      <c r="S38" s="26"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="26"/>
+      <c r="V38" s="26"/>
+      <c r="W38" s="26"/>
+      <c r="X38" s="26"/>
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
@@ -5030,13 +4653,13 @@
       <c r="D40" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="27" t="str">
+      <c r="E40" s="29" t="str">
         <f>IF(C39&lt;C40,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
       <c r="J40" t="s">
         <v>74</v>
       </c>
@@ -5143,13 +4766,13 @@
       <c r="L48" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="M48" s="27" t="str">
+      <c r="M48" s="29" t="str">
         <f>IF(K47&lt;K48,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 cannot be rejected</v>
       </c>
-      <c r="N48" s="27"/>
-      <c r="O48" s="27"/>
-      <c r="P48" s="27"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5163,18 +4786,18 @@
     <mergeCell ref="B11:H11"/>
   </mergeCells>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M48">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5305,33 +4928,33 @@
       <c r="F9" s="2"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="J11" s="26" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="J11" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="R11" s="26" t="s">
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="R11" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="26"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
@@ -6244,15 +5867,15 @@
       </c>
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
       <c r="J26" s="10">
         <v>13</v>
       </c>
@@ -6453,15 +6076,15 @@
       <c r="C30" s="20">
         <v>-102.71429999999999</v>
       </c>
-      <c r="J30" s="28" t="s">
+      <c r="J30" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="28"/>
-      <c r="P30" s="28"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
       <c r="R30" s="10">
         <v>17</v>
       </c>
@@ -6753,15 +6376,15 @@
         <f>K31-C27</f>
         <v>4</v>
       </c>
-      <c r="R38" s="28" t="s">
+      <c r="R38" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-      <c r="U38" s="28"/>
-      <c r="V38" s="28"/>
-      <c r="W38" s="28"/>
-      <c r="X38" s="28"/>
+      <c r="S38" s="26"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="26"/>
+      <c r="V38" s="26"/>
+      <c r="W38" s="26"/>
+      <c r="X38" s="26"/>
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
@@ -6797,13 +6420,13 @@
       <c r="D40" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E40" s="27" t="str">
+      <c r="E40" s="29" t="str">
         <f>IF(C39&lt;C40,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
       <c r="J40" s="1" t="s">
         <v>67</v>
       </c>
@@ -6869,13 +6492,13 @@
       <c r="L44" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="M44" s="27" t="str">
+      <c r="M44" s="29" t="str">
         <f>IF(K43&lt;K44,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 cannot be rejected</v>
       </c>
-      <c r="N44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="P44" s="27"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="29"/>
       <c r="R44" t="s">
         <v>74</v>
       </c>
@@ -6893,28 +6516,28 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="R38:X38"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="M44:P44"/>
     <mergeCell ref="J11:P11"/>
     <mergeCell ref="R11:X11"/>
     <mergeCell ref="J30:P30"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="B26:H26"/>
-    <mergeCell ref="R38:X38"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="M44:P44"/>
   </mergeCells>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M44">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6925,7 +6548,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D13E40A-665F-B04D-9859-142D9765DFCD}">
   <sheetPr>
-    <tabColor rgb="FF00B0F0"/>
+    <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="B2:P39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -7020,24 +6643,24 @@
       <c r="F8" s="2"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="J10" s="26" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="J10" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" s="11" t="s">
@@ -7612,15 +7235,15 @@
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
       <c r="J24" s="10">
         <v>12</v>
       </c>
@@ -7848,26 +7471,26 @@
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="J32" s="28" t="s">
+      <c r="J32" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
       <c r="J33" t="s">
         <v>69</v>
       </c>
@@ -7941,13 +7564,13 @@
       <c r="D38" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="27" t="str">
+      <c r="E38" s="29" t="str">
         <f>IF(C37&lt;C38,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 cannot be rejected</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
       <c r="J38" t="s">
         <v>74</v>
       </c>
@@ -7973,10 +7596,10 @@
     <mergeCell ref="J10:P10"/>
   </mergeCells>
   <conditionalFormatting sqref="E38:H38">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8071,24 +7694,24 @@
       <c r="F7" s="2"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="J9" s="26" t="s">
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="J9" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B10" s="11" t="s">
@@ -8619,15 +8242,15 @@
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
       <c r="J22" s="10">
         <v>11</v>
       </c>
@@ -8744,15 +8367,15 @@
       <c r="C26" s="20">
         <v>-136.6482</v>
       </c>
-      <c r="J26" s="28" t="s">
+      <c r="J26" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
@@ -8822,15 +8445,15 @@
       <c r="O30" s="12"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
       <c r="J31" t="s">
         <v>73</v>
       </c>
@@ -8903,13 +8526,13 @@
       <c r="D36" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="27" t="str">
+      <c r="E36" s="29" t="str">
         <f>IF(C35&lt;C36,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -9041,24 +8664,24 @@
       <c r="F7" s="2"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="J9" s="26" t="s">
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="J9" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B10" s="11" t="s">
@@ -9589,15 +9212,15 @@
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
       <c r="J22" s="2">
         <v>11</v>
       </c>
@@ -9714,15 +9337,15 @@
       <c r="C26" s="20">
         <v>-112.8862</v>
       </c>
-      <c r="J26" s="28" t="s">
+      <c r="J26" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
@@ -9792,15 +9415,15 @@
       <c r="O30" s="12"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
       <c r="J31" t="s">
         <v>73</v>
       </c>
@@ -9873,13 +9496,13 @@
       <c r="D36" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="27" t="str">
+      <c r="E36" s="29" t="str">
         <f>IF(C35&lt;C36,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -9905,18 +9528,18 @@
     <mergeCell ref="B9:H9"/>
   </mergeCells>
   <conditionalFormatting sqref="E36:H36">
-    <cfRule type="cellIs" dxfId="75" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M40:P40">
-    <cfRule type="cellIs" dxfId="73" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10036,33 +9659,33 @@
       <c r="F8" s="2"/>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="J10" s="26" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="J10" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="R10" s="26" t="s">
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="R10" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B11" s="11" t="s">
@@ -10910,15 +10533,15 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
       <c r="J24" s="2">
         <v>12</v>
       </c>
@@ -11119,15 +10742,15 @@
       <c r="C28" s="20">
         <v>-262.351</v>
       </c>
-      <c r="J28" s="28" t="s">
+      <c r="J28" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
       <c r="R28" s="2">
         <v>16</v>
       </c>
@@ -11279,26 +10902,26 @@
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
-      <c r="R32" s="28" t="s">
+      <c r="R32" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="26"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="26"/>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
       <c r="J33" t="s">
         <v>73</v>
       </c>
@@ -11377,15 +11000,15 @@
         <f>-2*(C28-K32)</f>
         <v>121.72300000000001</v>
       </c>
-      <c r="J37" s="29" t="s">
+      <c r="J37" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
       <c r="R37" t="s">
         <v>73</v>
       </c>
@@ -11404,13 +11027,13 @@
       <c r="D38" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="27" t="str">
+      <c r="E38" s="29" t="str">
         <f>IF(C37&lt;C38,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
       <c r="J38" s="30" t="s">
         <v>67</v>
       </c>
@@ -11463,16 +11086,19 @@
       <c r="L42" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="M42" s="27" t="str">
+      <c r="M42" s="29" t="str">
         <f>IF(K41&lt;K42,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="R10:X10"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="J10:P10"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="R32:X32"/>
     <mergeCell ref="B24:H24"/>
@@ -11481,23 +11107,20 @@
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="J38:P38"/>
-    <mergeCell ref="R10:X10"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="J10:P10"/>
   </mergeCells>
   <conditionalFormatting sqref="E38:H38">
-    <cfRule type="cellIs" dxfId="69" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42:P42">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11617,33 +11240,33 @@
       <c r="F8" s="2"/>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="J10" s="26" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="J10" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="R10" s="26" t="s">
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="R10" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B11" s="11" t="s">
@@ -12491,15 +12114,15 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
       <c r="J24" s="10">
         <v>12</v>
       </c>
@@ -12700,15 +12323,15 @@
       <c r="C28" s="20">
         <v>-221.21440000000001</v>
       </c>
-      <c r="J28" s="28" t="s">
+      <c r="J28" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
       <c r="R28" s="10">
         <v>16</v>
       </c>
@@ -12860,26 +12483,26 @@
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
-      <c r="R32" s="28" t="s">
+      <c r="R32" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="26"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="26"/>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
       <c r="J33" t="s">
         <v>73</v>
       </c>
@@ -12958,15 +12581,15 @@
         <f>-2*(C28-K32)</f>
         <v>58.163000000000011</v>
       </c>
-      <c r="J37" s="29" t="s">
+      <c r="J37" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
       <c r="R37" t="s">
         <v>73</v>
       </c>
@@ -12985,13 +12608,13 @@
       <c r="D38" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="27" t="str">
+      <c r="E38" s="29" t="str">
         <f>IF(C37&lt;C38,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
       <c r="J38" s="30" t="s">
         <v>67</v>
       </c>
@@ -13044,16 +12667,19 @@
       <c r="L42" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="M42" s="27" t="str">
+      <c r="M42" s="29" t="str">
         <f>IF(K41&lt;K42,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="R10:X10"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="J10:P10"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="R32:X32"/>
     <mergeCell ref="B24:H24"/>
@@ -13062,23 +12688,20 @@
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="J38:P38"/>
-    <mergeCell ref="R10:X10"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="J10:P10"/>
   </mergeCells>
   <conditionalFormatting sqref="E38:H38">
-    <cfRule type="cellIs" dxfId="61" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42:P42">
-    <cfRule type="cellIs" dxfId="57" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13184,24 +12807,24 @@
       <c r="F8" s="2"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="J10" s="26" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="J10" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11" s="11" t="s">
@@ -13776,15 +13399,15 @@
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
       <c r="J24" s="10">
         <v>12</v>
       </c>
@@ -14012,26 +13635,26 @@
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="J32" s="28" t="s">
+      <c r="J32" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
       <c r="J33" t="s">
         <v>69</v>
       </c>
@@ -14105,13 +13728,13 @@
       <c r="D38" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="27" t="str">
+      <c r="E38" s="29" t="str">
         <f>IF(C37&lt;C38,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
       <c r="J38" t="s">
         <v>74</v>
       </c>
@@ -14137,10 +13760,10 @@
     <mergeCell ref="J10:P10"/>
   </mergeCells>
   <conditionalFormatting sqref="E38:H38">
-    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14224,24 +13847,24 @@
       <c r="F6" s="2"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B8" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="J8" s="26" t="s">
+      <c r="B8" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="J8" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B9" s="11" t="s">
@@ -14728,24 +14351,24 @@
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="J20" s="28" t="s">
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="J20" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
@@ -14868,15 +14491,15 @@
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
@@ -14924,13 +14547,13 @@
       <c r="D34" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="27" t="str">
+      <c r="E34" s="29" t="str">
         <f>IF(C33&lt;C34,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 cannot be rejected</v>
       </c>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -14956,18 +14579,18 @@
     <mergeCell ref="J8:P8"/>
   </mergeCells>
   <conditionalFormatting sqref="E34:H34">
-    <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M38:P38">
-    <cfRule type="cellIs" dxfId="47" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15087,33 +14710,33 @@
       <c r="F8" s="2"/>
     </row>
     <row r="10" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="J10" s="26" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="J10" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="R10" s="26" t="s">
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="R10" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
     </row>
     <row r="11" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B11" s="11" t="s">
@@ -15961,15 +15584,15 @@
       </c>
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
       <c r="J24" s="10">
         <v>12</v>
       </c>
@@ -16170,15 +15793,15 @@
       <c r="C28" s="20">
         <v>-92.279290000000003</v>
       </c>
-      <c r="J28" s="28" t="s">
+      <c r="J28" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
       <c r="R28" s="10">
         <v>16</v>
       </c>
@@ -16330,26 +15953,26 @@
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
-      <c r="R32" s="28" t="s">
+      <c r="R32" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="26"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="26"/>
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
       <c r="J33" t="s">
         <v>73</v>
       </c>
@@ -16428,15 +16051,15 @@
         <f>-2*(C28-K32)</f>
         <v>20.251720000000006</v>
       </c>
-      <c r="J37" s="29" t="s">
+      <c r="J37" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
       <c r="R37" t="s">
         <v>73</v>
       </c>
@@ -16455,13 +16078,13 @@
       <c r="D38" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="27" t="str">
+      <c r="E38" s="29" t="str">
         <f>IF(C37&lt;C38,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
       <c r="J38" s="30" t="s">
         <v>67</v>
       </c>
@@ -16514,16 +16137,19 @@
       <c r="L42" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="M42" s="27" t="str">
+      <c r="M42" s="29" t="str">
         <f>IF(K41&lt;K42,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="R10:X10"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="J10:P10"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="J28:P28"/>
@@ -16532,23 +16158,20 @@
     <mergeCell ref="J37:P37"/>
     <mergeCell ref="E38:H38"/>
     <mergeCell ref="J38:P38"/>
-    <mergeCell ref="R10:X10"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="J10:P10"/>
   </mergeCells>
   <conditionalFormatting sqref="E38:H38">
-    <cfRule type="cellIs" dxfId="43" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M42:P42">
-    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16643,24 +16266,24 @@
       <c r="F7" s="2"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="J9" s="26" t="s">
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="J9" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B10" s="11" t="s">
@@ -17191,15 +16814,15 @@
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
       <c r="J22" s="10">
         <v>11</v>
       </c>
@@ -17316,15 +16939,15 @@
       <c r="C26" s="20">
         <v>-141.95429999999999</v>
       </c>
-      <c r="J26" s="28" t="s">
+      <c r="J26" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
@@ -17394,15 +17017,15 @@
       <c r="O30" s="12"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
       <c r="J31" t="s">
         <v>73</v>
       </c>
@@ -17475,13 +17098,13 @@
       <c r="D36" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="27" t="str">
+      <c r="E36" s="29" t="str">
         <f>IF(C35&lt;C36,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 rejected</v>
       </c>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -17507,18 +17130,18 @@
     <mergeCell ref="J9:P9"/>
   </mergeCells>
   <conditionalFormatting sqref="E36:H36">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M40:P40">
-    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17602,24 +17225,24 @@
       <c r="F6" s="2"/>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B8" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="J8" s="26" t="s">
+      <c r="B8" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="J8" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B9" s="11" t="s">
@@ -18106,24 +17729,24 @@
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="J20" s="28" t="s">
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="J20" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
@@ -18246,15 +17869,15 @@
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
@@ -18302,13 +17925,13 @@
       <c r="D34" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="27" t="str">
+      <c r="E34" s="29" t="str">
         <f>IF(C33&lt;C34,"H0 cannot be rejected","H0 rejected")</f>
         <v>H0 cannot be rejected</v>
       </c>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -18334,18 +17957,18 @@
     <mergeCell ref="J8:P8"/>
   </mergeCells>
   <conditionalFormatting sqref="E34:H34">
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M38:P38">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"H0 cannot be rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"H0 rejected"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Flexibility_Preferences.xlsx
+++ b/Flexibility_Preferences.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DC4D99-F2AC-A84E-8A62-5115E8963B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19940" xr2:uid="{ADD43ED2-A73A-FE49-A984-2AB27DA5AEBD}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19940" activeTab="13" xr2:uid="{ADD43ED2-A73A-FE49-A984-2AB27DA5AEBD}"/>
   </bookViews>
   <sheets>
     <sheet name="House_01" sheetId="14" r:id="rId1"/>
